--- a/human_validation/judge/kor/judge_D009_S004_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D009_S004_P002__claude-sonnet-5_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,166 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 저는 이 선생님입니다. 먼저, 오늘 어떤 일로 오시게 되었는지 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제가 온 이유는, 공장에서 재설계 프로젝트를 계속 쏟아내고, 퇴근 후에도 공급업체에 전화하고, 교대 근무 계획도 직접 다시 짜고—그냥 그 모든 걸 다 떠맡았거든요. 그러다 갑자기 제가 벌여놓은 그 계획들을 도저히 따라갈 수가 없게 됐어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 이렇게 에너지가 넘치고 프로젝트를 끊임없이 벌이던 시기가 얼마나 지속됐나요? 며칠, 몇 주, 아니면 그보다 길었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 임시 아파트로 이사한 뒤로 한 3주 정도 계속됐어요—그렇게 과열되어 있다가 이제는 제대로 기능하기도 힘든 상태예요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 그렇게 에너지가 넘쳤던 3주 동안, 몇 시간밖에 못 자도 충분히 쉬었고 힘이 넘친다고 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네. 밤에 두세 시간 정도밖에 안 잤는데도 공장에 가면 정신이 또렷하고 힘이 넘쳤어요. 잠은 그냥 선택 사항 같았어요—오히려 비효율적으로 느껴질 정도였죠.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 그 3주 동안, 평소의 자신을 훨씬 뛰어넘는 능력이나 아이디어, 중요성을 가진 것처럼 유난히 자신감이 넘치거나 특별하다고 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 네. 솔직히 제가 컨설팅팀보다 더 빨리 전체 생산 공정을 고칠 수 있다고 생각했어요. 사람들이 우려를 제기해도 그냥 무시해 버렸어요—그때는 실패라는 게 저한테는 있을 수 없는 일처럼 느껴졌거든요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 지난 3주 전에도, 이와 비슷하게 에너지가 넘쳤던 시기나, 반대로 몇 주간 유난히 우울하고 가라앉고 절망적이었던 시기가 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 네. 그 전에 한 3개월 정도 정말 심하게 우울했던 시기가 있었어요. 이사하고 공장에 배치된 게 그걸 감당하기 더 힘들게 만들었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 에너지가 넘쳤던 그 3주 동안, 다른 사람들은 듣지 못하는 목소리나 소리를 들으신 적이 있나요? 아니면 특별한 임무를 위해 선택받았다거나 초능력이 있다는 것처럼, 다른 사람들이 비현실적이라고 여기거나 설득하려 했던 믿음을 가지신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 아니요, 목소리 같은 건 안 들렸어요. 스스로에 대한 확신은 아주 강했지만, 제가 초능력이 있다거나 특별한 임무가 있다고 생각하진 않았어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 그 3주 동안, 이렇게 에너지가 넘쳤던 시기가 직장에서의 갈등이나 위험한 결정, 다른 사람들이 개입하게 만들거나 입원이 필요할 정도의 심각한 문제를 일으켰나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 네. 교대 근무 계획 회의를 제대로 진행할 수가 없어서 빠지게 해달라고 요청해야 했어요. 산업보건팀도 개입했는데, 제 업무에 필요한 기본적인 생산 관련 결정조차 내릴 수 없었거든요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>진단명: 제2형 양극성장애 (D009)
 인구통계: 성별 여성 / 나이 29 / 직업상태 industrial production manager / 최종학력 대학원 졸업
@@ -575,224 +726,45 @@
 증상 지속 기간: None
 추가 요건: 
 주호소 증상 코드: S040
-배경 서술: 지아치 왕은 익숙했던 시카고 동네를 떠나, 자신이 전면 개편을 맡은 제조 공장 근처의 임시 아파트로 이사하면서 차이나타운에서의 가족 모임, 평소 다니던 운동 모임, 그리고 그녀의 업무 강도를 잡아주던 비공식적인 지지 관계들로부터 단절되었다. 처음에 그녀는 이사와 공장 재설계에 유난히 넘치는 자신감으로 몰두하며, 회의에서 빠르게 말하고, 잠을 거의 자지 않고, 동료들이 인상적이라고 여기면서도 따라가기 힘들어할 만큼 새로운 개선 계획들을 쏟아냈다. 3주 안에 그 추진력은 지속적인 우울한 기분, 불규칙한 식사, 수면 장애, 그리고 느려짐과 초조함이 번갈아 나타나는 상태, 일상적인 생산 관련 결정을 내리는 데의 어려움으로 무너져 내렸고, 결국 그녀가 생각을 명확하게 할 수 없다는 이유로 교대 근무 계획 회의에서 빠지겠다고 요청한 뒤 산업보건팀에 의뢰되었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 저는 이 선생님입니다. 먼저, 오늘 어떤 일로 오시게 되었는지 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제가 온 이유는, 공장에서 재설계 프로젝트를 계속 쏟아내고, 퇴근 후에도 공급업체에 전화하고, 교대 근무 계획도 직접 다시 짜고—그냥 그 모든 걸 다 떠맡았거든요. 그러다 갑자기 제가 벌여놓은 그 계획들을 도저히 따라갈 수가 없게 됐어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 이렇게 에너지가 넘치고 프로젝트를 끊임없이 벌이던 시기가 얼마나 지속됐나요? 며칠, 몇 주, 아니면 그보다 길었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 임시 아파트로 이사한 뒤로 한 3주 정도 계속됐어요—그렇게 과열되어 있다가 이제는 제대로 기능하기도 힘든 상태예요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 그렇게 에너지가 넘쳤던 3주 동안, 몇 시간밖에 못 자도 충분히 쉬었고 힘이 넘친다고 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네. 밤에 두세 시간 정도밖에 안 잤는데도 공장에 가면 정신이 또렷하고 힘이 넘쳤어요. 잠은 그냥 선택 사항 같았어요—오히려 비효율적으로 느껴질 정도였죠.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 그 3주 동안, 평소의 자신을 훨씬 뛰어넘는 능력이나 아이디어, 중요성을 가진 것처럼 유난히 자신감이 넘치거나 특별하다고 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 네. 솔직히 제가 컨설팅팀보다 더 빨리 전체 생산 공정을 고칠 수 있다고 생각했어요. 사람들이 우려를 제기해도 그냥 무시해 버렸어요—그때는 실패라는 게 저한테는 있을 수 없는 일처럼 느껴졌거든요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 지난 3주 전에도, 이와 비슷하게 에너지가 넘쳤던 시기나, 반대로 몇 주간 유난히 우울하고 가라앉고 절망적이었던 시기가 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 네. 그 전에 한 3개월 정도 정말 심하게 우울했던 시기가 있었어요. 이사하고 공장에 배치된 게 그걸 감당하기 더 힘들게 만들었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 에너지가 넘쳤던 그 3주 동안, 다른 사람들은 듣지 못하는 목소리나 소리를 들으신 적이 있나요? 아니면 특별한 임무를 위해 선택받았다거나 초능력이 있다는 것처럼, 다른 사람들이 비현실적이라고 여기거나 설득하려 했던 믿음을 가지신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 아니요, 목소리 같은 건 안 들렸어요. 스스로에 대한 확신은 아주 강했지만, 제가 초능력이 있다거나 특별한 임무가 있다고 생각하진 않았어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 그 3주 동안, 이렇게 에너지가 넘쳤던 시기가 직장에서의 갈등이나 위험한 결정, 다른 사람들이 개입하게 만들거나 입원이 필요할 정도의 심각한 문제를 일으켰나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 네. 교대 근무 계획 회의를 제대로 진행할 수가 없어서 빠지게 해달라고 요청해야 했어요. 산업보건팀도 개입했는데, 제 업무에 필요한 기본적인 생산 관련 결정조차 내릴 수 없었거든요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
+배경 서술: 지아치 왕은 익숙했던 시카고 동네를 떠나, 자신이 전면 개편을 맡은 제조 공장 근처의 임시 아파트로 이사하면서 차이나타운에서의 가족 모임, 평소 다니던 운동 모임, 그리고 그녀의 업무 강도를 잡아주던 비공식적인 지지 관계들로부터 단절되었다. 처음에 그녀는 이사와 공장 재설계에 유난히 넘치는 자신감으로 몰두하며, 회의에서 빠르게 말하고, 잠을 거의 자지 않고, 동료들이 인상적이라고 여기면서도 따라가기 힘들어할 만큼 새로운 개선 계획들을 쏟아냈다. 3주 안에 그 추진력은 지속적인 우울한 기분, 불규칙한 식사, 수면 장애, 그리고 느려짐과 초조함이 번갈아 나타나는 상태, 일상적인 생산 관련 결정을 내리는 데의 어려움으로 무너져 내렸고, 결국 그녀가 생각을 명확하게 할 수 없다는 이유로 교대 근무 계획 회의에서 빠지겠다고 요청한 뒤 산업보건팀에 의뢰되었다.
+표집된 증상 목록:
+  - S024 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - S026 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.
+  - S027 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - S028 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.
+  - S031 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.
+  - S033 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.
+  - S034 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.
+  - S035 과장된 자존감: 과장된 자존감이나 과대성(단순한 자신감 과잉부터 망상적 수준까지 다양할 수 있음).
+  - S036 수면 욕구 감소: 수면 욕구가 감소함(예: 단 3시간만 자도 개운함을 느낌).
+  - S037 압박된 언어: 평소보다 말이 많아지거나 계속 말하려는 압박감을 느낌.
+  - S040 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.</t>
+        </is>
+      </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>[7번째 턴 · 의사의 감별진단] 중간확률: 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: None (None, ICD: F31.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: hypomanic_episode (관계=must_include, 요구개수=5, 충족개수=4, 커버리지=0.8)
-  확인된 근거: 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.; 과장된 자존감: 과장된 자존감이나 과대성(단순한 자신감 과잉부터 망상적 수준까지 다양할 수 있음).; 수면 욕구 감소: 수면 욕구가 감소함(예: 단 3시간만 자도 개운함을 느낌).; 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.
-  누락: 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.; 압박된 언어: 평소보다 말이 많아지거나 계속 말하려는 압박감을 느낌.; 사고의 질주: 사고의 비약이나 생각이 질주하는 듯한 주관적 경험.; 조증성 산만함: 중요하지 않거나 관련 없는 외부 자극에 지나치게 쉽게 주의가 쏠림.; 위험 결과 초래 행동: 고통스러운 결과를 초래할 가능성이 높은 활동에 지나치게 몰두함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: depressive_episode (관계=must_include, 요구개수=5, 충족개수=1, 커버리지=0.2)
-  확인된 근거: 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
-  누락: 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.; 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.; 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.; 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
+          <t>의사의 최종 진단: None (None, ICD: F31.1)
+지속 기간 요건: None
+기능적 손상 요건: None
+추가 요건: None
+체크리스트 그룹: hypomanic_episode (관계=must_include, 요구개수=5, 충족개수=4, 커버리지=0.8)
+확인된 근거:
+  - 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.
+  - 과장된 자존감: 과장된 자존감이나 과대성(단순한 자신감 과잉부터 망상적 수준까지 다양할 수 있음).
+  - 수면 욕구 감소: 수면 욕구가 감소함(예: 단 3시간만 자도 개운함을 느낌).
+  - 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.
+체크리스트 그룹: depressive_episode (관계=must_include, 요구개수=5, 충족개수=1, 커버리지=0.2)
+확인된 근거:
+  - 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A37:B37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D009_S004_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D009_S004_P002__claude-sonnet-5_kor.xlsx
@@ -712,6 +712,11 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -760,11 +765,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A37:B37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D009_S004_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D009_S004_P002__claude-sonnet-5_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
